--- a/data/آذین 2/cnc/machines.xlsx
+++ b/data/آذین 2/cnc/machines.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayarat-d\Desktop\app\my-crossplatform-app\data\آذین 2\cnc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayarat-d\Desktop\app\my-crossplatform-app\data\cnc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF1D22E-5C22-4D04-830F-A052C06456DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC06102F-87FE-4FE3-BFA1-024DB9D81F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,128 @@
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+  <si>
+    <t>CV0601</t>
+  </si>
+  <si>
+    <t>CV0602</t>
+  </si>
+  <si>
+    <t>CV0603</t>
+  </si>
+  <si>
+    <t>CV0604</t>
+  </si>
+  <si>
+    <t>CV0605</t>
+  </si>
+  <si>
+    <t>CV0606</t>
+  </si>
+  <si>
+    <t>CV0607</t>
+  </si>
+  <si>
+    <t>CV0608</t>
+  </si>
+  <si>
+    <t>CT0601</t>
+  </si>
+  <si>
+    <t>CT0610</t>
+  </si>
+  <si>
+    <t>CT0602</t>
+  </si>
+  <si>
+    <t>CT0603</t>
+  </si>
+  <si>
+    <t>CT0604</t>
+  </si>
+  <si>
+    <t>CT0605</t>
+  </si>
+  <si>
+    <t>CT0606</t>
+  </si>
+  <si>
+    <t>CT0607</t>
+  </si>
+  <si>
+    <t>CT0608</t>
+  </si>
+  <si>
+    <t>CT0609</t>
+  </si>
+  <si>
+    <t>CT0611</t>
+  </si>
+  <si>
+    <t>CT0612</t>
+  </si>
+  <si>
+    <t>GD0601</t>
+  </si>
+  <si>
+    <t>GD0602</t>
+  </si>
+  <si>
+    <t>BB0601</t>
+  </si>
+  <si>
+    <t>BB0602</t>
+  </si>
+  <si>
+    <t>BB0603</t>
+  </si>
+  <si>
+    <t>BB0604</t>
+  </si>
+  <si>
+    <t>BB0605</t>
+  </si>
+  <si>
+    <t>BB0606</t>
+  </si>
+  <si>
+    <t>BB0607</t>
+  </si>
+  <si>
+    <t>BB0608</t>
+  </si>
+  <si>
+    <t>BB0609</t>
+  </si>
+  <si>
+    <t>BB0610</t>
+  </si>
+  <si>
+    <t>BB0611</t>
+  </si>
+  <si>
+    <t>BB0612</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P </t>
+  </si>
+  <si>
+    <t>ML0601</t>
+  </si>
+  <si>
+    <t>ML0602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML </t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,157 +476,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-    </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
+      <c r="A4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2</v>
-      </c>
-    </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>222</v>
+      <c r="A24" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>2</v>
+      <c r="A25" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>2</v>
+      <c r="A26" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>2</v>
+      <c r="A27" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>2</v>
+      <c r="A28" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>22</v>
+      <c r="A29" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2</v>
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
